--- a/OpenCartManualTestingProject.xlsx
+++ b/OpenCartManualTestingProject.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alveera Hafeez\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D1707D3-029C-4FC9-B667-987EECFA5D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2816FDE9-2867-4D87-9B5B-678A8E830CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="18240" windowHeight="12336" activeTab="1" xr2:uid="{46EFE0BE-687D-4033-964F-31D299E0F498}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="18468" windowHeight="12336" activeTab="2" xr2:uid="{46EFE0BE-687D-4033-964F-31D299E0F498}"/>
   </bookViews>
   <sheets>
     <sheet name="TestScenario" sheetId="1" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="240">
   <si>
     <t>Client Name</t>
   </si>
@@ -713,6 +713,150 @@
   </si>
   <si>
     <t>Actual Result</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Bug  Title</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Expected Result</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>BUG- 001</t>
+  </si>
+  <si>
+    <t>TC- 005</t>
+  </si>
+  <si>
+    <t>Weak password accepted</t>
+  </si>
+  <si>
+    <t>Enter password "12345" and register</t>
+  </si>
+  <si>
+    <t>System should reject weak password</t>
+  </si>
+  <si>
+    <t>Account created successfully</t>
+  </si>
+  <si>
+    <t>Major</t>
+  </si>
+  <si>
+    <t>Open</t>
+  </si>
+  <si>
+    <t>BUG- 002</t>
+  </si>
+  <si>
+    <t>BUG- 003</t>
+  </si>
+  <si>
+    <t>BUG- 004</t>
+  </si>
+  <si>
+    <t>BUG- 005</t>
+  </si>
+  <si>
+    <t>BUG- 006</t>
+  </si>
+  <si>
+    <t>BUG- 007</t>
+  </si>
+  <si>
+    <t>TC- 015</t>
+  </si>
+  <si>
+    <t>TC- 016</t>
+  </si>
+  <si>
+    <t>TC- 017</t>
+  </si>
+  <si>
+    <t>TC- 018</t>
+  </si>
+  <si>
+    <t>TC- 019</t>
+  </si>
+  <si>
+    <t>TC- 022</t>
+  </si>
+  <si>
+    <t>First  name accepts numbers</t>
+  </si>
+  <si>
+    <t>Last name aceepts numbers</t>
+  </si>
+  <si>
+    <t>Numbers allowed after space in first name</t>
+  </si>
+  <si>
+    <t>Numbers allowed after space in last name</t>
+  </si>
+  <si>
+    <t>Special character allowed in first name</t>
+  </si>
+  <si>
+    <t>TC- 020</t>
+  </si>
+  <si>
+    <t>Special character allowed in last name</t>
+  </si>
+  <si>
+    <t>BUG- 008</t>
+  </si>
+  <si>
+    <t>Password longer than limit accepted</t>
+  </si>
+  <si>
+    <t>Enter First Name: admin12</t>
+  </si>
+  <si>
+    <t>Enter Last Name: class12</t>
+  </si>
+  <si>
+    <t>Enter First Name:admin 12</t>
+  </si>
+  <si>
+    <t>Enter Last Name: class 12</t>
+  </si>
+  <si>
+    <t>Enter First Name:admin@</t>
+  </si>
+  <si>
+    <t>Enter Last Name:class@</t>
+  </si>
+  <si>
+    <t>Enter password &gt; 20 characters</t>
+  </si>
+  <si>
+    <t>Numbers should not be allowed</t>
+  </si>
+  <si>
+    <t>System should show validation error</t>
+  </si>
+  <si>
+    <t>Special characters should not be allowed</t>
+  </si>
+  <si>
+    <t>System should reject password</t>
+  </si>
+  <si>
+    <t>Minor</t>
+  </si>
+  <si>
+    <t>&gt;&gt;Register</t>
   </si>
 </sst>
 </file>
@@ -828,26 +972,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -856,6 +987,25 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1206,59 +1356,59 @@
       <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="11"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="6"/>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C3" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="D3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="10"/>
-      <c r="F3" s="11"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="6"/>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="11"/>
+      <c r="D4" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D5" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="11"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="11"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="C7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="9"/>
-      <c r="E7" s="10"/>
-      <c r="F7" s="11"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
@@ -1715,758 +1865,780 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+      <c r="A1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="8"/>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
     </row>
     <row r="3" spans="1:11" ht="90" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="9" t="s">
         <v>89</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="5" t="s">
+      <c r="I3" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K3" s="2"/>
     </row>
     <row r="4" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="11" t="s">
         <v>118</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K4" s="2"/>
     </row>
     <row r="5" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K5" s="2"/>
     </row>
     <row r="6" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K6" s="2"/>
     </row>
     <row r="7" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="10" t="s">
         <v>121</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="10" t="s">
         <v>129</v>
       </c>
+      <c r="K7" s="2"/>
     </row>
     <row r="8" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K8" s="2"/>
     </row>
     <row r="9" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="9" t="s">
         <v>113</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K9" s="2"/>
     </row>
     <row r="10" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K11" s="2"/>
     </row>
     <row r="12" spans="1:11" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="9" t="s">
         <v>111</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="10" t="s">
         <v>141</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K12" s="2"/>
     </row>
     <row r="13" spans="1:11" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K13" s="2"/>
     </row>
     <row r="14" spans="1:11" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C14" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K14" s="2"/>
     </row>
     <row r="15" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="11" t="s">
         <v>108</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="10" t="s">
         <v>128</v>
       </c>
+      <c r="K15" s="2"/>
     </row>
     <row r="16" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="11" t="s">
         <v>107</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="11" t="s">
         <v>151</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="10" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="17" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B17" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="18" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="4" t="s">
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B18" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="F18" s="6" t="s">
+      <c r="F18" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="19" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B19" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="11" t="s">
         <v>162</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="20" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A20" s="4" t="s">
+      <c r="K19" s="2"/>
+    </row>
+    <row r="20" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B20" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F20" s="6" t="s">
+      <c r="F20" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="21" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="4" t="s">
+      <c r="K20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A21" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B21" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="9" t="s">
         <v>176</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="F21" s="6" t="s">
+      <c r="F21" s="11" t="s">
         <v>181</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="22" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="4" t="s">
+      <c r="K21" s="2"/>
+    </row>
+    <row r="22" spans="1:11" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B22" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="9" t="s">
         <v>177</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="11" t="s">
         <v>183</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="10" t="s">
         <v>129</v>
       </c>
-    </row>
-    <row r="23" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="4" t="s">
+      <c r="K22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="9" t="s">
         <v>178</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="11" t="s">
         <v>184</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="10" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="24" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="4" t="s">
+      <c r="K23" s="2"/>
+    </row>
+    <row r="24" spans="1:11" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B24" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="9" t="s">
         <v>179</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="11" t="s">
         <v>185</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="10" t="s">
         <v>129</v>
       </c>
+      <c r="K24" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2482,9 +2654,272 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8E71ABD-E2B6-43F3-BC8B-96F975007030}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="3" width="24.5546875" customWidth="1"/>
+    <col min="4" max="4" width="30.109375" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" customWidth="1"/>
+    <col min="7" max="7" width="17.21875" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="7" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G5" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G6" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G7" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H7" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G8" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H8" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="37.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="G10" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="H10" s="13" t="s">
+        <v>205</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Register!A1" display="&gt;&gt;Register" xr:uid="{3E921384-3322-4152-A549-A438E03B07F4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
